--- a/02_DIA_inicio_2026_analisis_assets/rbd_9415_escuela-territorio-antartico_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9415_escuela-territorio-antartico_nt2_nucleos.xlsx
@@ -763,13 +763,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72A587DA-6956-48B4-A613-6EB0C0162EE4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B0620C9-CA12-480E-9841-A795BC4CF60E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{358A984A-7E4F-45B3-A107-75CB9BA0F025}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35D887FA-52FB-4913-8287-874DC37B75AF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44615D18-2245-4AE8-BB66-34D0BC184039}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFBD4637-7605-49FE-A714-4C5D7F2587FD}"/>
 </file>